--- a/光伏配储项目/电价数据/2026/文旅站.xlsx
+++ b/光伏配储项目/电价数据/2026/文旅站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50864</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38427</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.74261</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5718</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5802200000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5026499999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.49494</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43735</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45413</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43039</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42204</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40839</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39716</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39733</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42286</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41235</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39133</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41676</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42049</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41373</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42371</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41207</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44281</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27208</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11597</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09434000000000001</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.10268</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.08679000000000001</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.11265</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03572</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.0788</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.09295</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.09525</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.06466</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08985</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.03761</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.03417</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.0276</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14204</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21257</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22001</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.21941</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21122</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.01124</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.22309</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11891</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.24364</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.26586</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.27977</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.24093</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.17902</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.25904</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.52478</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.41071</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.48522</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.71633</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39264</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.60015</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42742</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43544</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42022</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.57072</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.45124</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6041</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79065</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6409900000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6061</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.73407</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.87146</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41816</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.66126</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5860599999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.66577</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.48705</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.43327</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.62319</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.60014</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47131</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40481</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42599</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.68853</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.15469</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.6694600000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.7313099999999999</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.70682</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.50261</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51764</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5047200000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50443</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48699</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46898</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39135</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4188</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49481</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.5700499999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.5524199999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.4291</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50845</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29347</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.07038</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.29859</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.47592</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.74311</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.95441</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.6719299999999999</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.47081</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.40488</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.16963</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28671</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.28731</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.47879</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.23441</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.24411</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.41408</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.3915</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.49382</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.5974299999999999</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.51118</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.66795</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.65622</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.71382</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.45076</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.43054</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.75509</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.44613</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.56516</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.42633</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.48167</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43398</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42746</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.39928</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33472</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50804</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.4042</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38361</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.39912</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38262</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42761</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.4431</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39659</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47393</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44331</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43766</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39411</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.20472</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.22458</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.20601</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.19291</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26733</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30035</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.48207</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.56671</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.49498</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.41678</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.1775</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.27869</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29603</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.39945</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.40363</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.45635</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.43391</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.48718</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.51519</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.5989099999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.5443600000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.6046</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.45261</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.41763</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.47149</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.39792</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.43629</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43304</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45249</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.43906</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.38941</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41341</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39626</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34202</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.41127</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.38241</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.29138</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39706</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40826</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3747799999999999</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.40434</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44754</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39791</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38847</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.40539</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.43277</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44439</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.25611</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.14721</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.23952</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.17017</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.26497</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.16794</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30212</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5664600000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.26476</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.07495</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.07504999999999999</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.09264</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.20231</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.21265</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6496000000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.07895999999999999</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.18236</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.29319</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.45899</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.41014</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.42474</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.29383</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.17127</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.39943</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.48288</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.48167</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5224</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.43015</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40922</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.40838</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.4308</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29309</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29998</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38197</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31778</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29202</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29658</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26561</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.05402000000000001</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.06856999999999999</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.05399</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.05232</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04481</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.07074</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.06473999999999999</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.06784999999999999</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.02679</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04596</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.01618</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.02269</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.01032</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.01692</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.02033</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.02208</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.006549999999999999</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.03691</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04213</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.01085</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.03642</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.03914</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.03861</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04509000000000001</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.0116</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.01727</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.2193</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.08054</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05927</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00389</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15724</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.02894</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09189</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29172</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37726</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.4007</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41016</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4679</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39678</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41799</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35135</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.65534</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44841</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42523</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42549</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04338</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04578</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04545</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.03379</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.03268</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.12479</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.00622</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.03741</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04372</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.0434</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03668</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04534000000000001</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525999999999999</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04359</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.02102</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.02308</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04473</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04998</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04988</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04742</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04795</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19969</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14268</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36503</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3356</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31711</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40488</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27112</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27085</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17234</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14768</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15941</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15856</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23608</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21397</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22648</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26881</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28562</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28039</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27056</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38325</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42812</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45639</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15656</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50766</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7853300000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78101</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92037</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91391</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8620800000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29573</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88666</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63144</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18625</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86834</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.54383</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03232</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5299400000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79028</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5318999999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7722599999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77698</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8766799999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87349</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49249</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39802</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39903</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44918</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20613</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87878</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55099</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62099</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5381</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49744</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.4557</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42414</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43698</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38795</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45266</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41973</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41499</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43407</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.4034700000000001</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58763</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4289</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5964400000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6032999999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6950499999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46788</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41939</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5821499999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8842899999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6349900000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8448600000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.82382</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86172</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44203</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.43718</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.26324</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41127</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41393</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45403</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41631</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39255</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35379</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9190700000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.4664</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.37209</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41013</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46725</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38165</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41097</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5021600000000001</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38871</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37151</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30758</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28884</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29685</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16414</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26204</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19895</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27734</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19342</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27854</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25569</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27654</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38648</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.44724</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.41254</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4233</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.45089</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42148</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40284</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40162</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.6001799999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89125</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.36417</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.166</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70113</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79215</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.66879</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5854199999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45383</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45147</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50193</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44101</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41602</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41385</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4251</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50357</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41384</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43513</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41469</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43527</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39116</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.43019</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45293</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39714</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42445</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43634</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41384</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41376</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40196</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42571</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40452</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49576</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29684</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.54243</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24959</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.11762</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27263</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.26993</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26199</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25537</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2825299999999999</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28464</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28935</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40417</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40165</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57139</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46445</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.86925</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46686</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43826</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42999</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38637</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32456</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39316</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37644</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28435</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27536</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.28958</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27567</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22066</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.13713</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14226</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27957</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15058</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14172</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.13492</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14075</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13362</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24203</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13384</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25103</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.25345</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.1325</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.09185</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10515</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10533</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.11638</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.13246</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.13679</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27162</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39913</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45119</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39166</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39797</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44105</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4402799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44525</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39759</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39142</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5412</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47039</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42481</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41685</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.3816000000000001</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39359</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38129</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39232</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38149</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27303</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26729</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19483</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24787</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24239</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27134</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30102</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29121</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28502</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24251</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.41449</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.26148</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41623</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38135</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38616</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36082</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42036</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39414</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.28964</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39659</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43867</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42709</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.06239</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25151</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.25244</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.09412000000000001</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.2287</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.28724</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.2863</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.28548</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41282</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43424</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41534</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6890599999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5078199999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.21924</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.29257</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28375</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.29734</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.46971</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.46175</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.45363</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.4607</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.45482</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.46617</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.5314500000000001</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38693</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.45918</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.44454</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.35001</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38292</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.47493</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41183</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6565800000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.77759</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45351</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28136</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45979</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41138</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36623</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26594</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14832</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28648</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28402</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19806</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25964</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27822</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.30593</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27957</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21441</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25291</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28428</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27614</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28922</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28934</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.16269</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29187</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.28813</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43837</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.47483</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6999099999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6554800000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6677799999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.5522400000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.89512</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.49467</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.88248</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.53113</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.52383</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.43417</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.39179</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.50792</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43197</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42025</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36068</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.4912</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.52946</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.4818</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48668</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.4178</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39835</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.4035899999999999</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41105</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41745</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39483</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41152</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40933</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39516</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42083</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41835</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40133</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41456</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45385</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45198</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5662999999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50505</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45386</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.49037</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.45104</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.4478</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38477</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.40239</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.43977</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.43004</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.52242</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43624</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.40433</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40997</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29649</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37312</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6263200000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.19207</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.28587</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37675</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.3728399999999999</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35348</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41335</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43757</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49477</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.44033</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5618200000000001</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.14082</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.60409</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.75342</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7754099999999999</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.05299</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.30534</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.81348</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.58621</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52689</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.83816</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7689199999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6233200000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67169</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44067</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47265</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.4841</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47881</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47123</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41833</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55431</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42901</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44319</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45721</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43424</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42437</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44696</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45704</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40586</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39773</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36708</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40084</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39719</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38736</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.18739</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38514</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40827</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46202</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40284</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.47135</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.10749</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18273</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37461</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38161</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37606</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41898</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.37311</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4335</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41643</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41665</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39392</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.41184</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.41172</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40106</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39837</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.3679</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44719</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39514</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38328</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30551</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27049</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22916</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28724</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22844</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28618</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24799</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.24416</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.14339</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24706</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04382</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25019</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27721</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16694</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18569</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27419</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.2331</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25887</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26267</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23646</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27743</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28504</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28768</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36267</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36423</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.36176</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35131</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31445</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.22648</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.29129</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.27215</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01824</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00036</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00747</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15732</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.03135</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03965</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01492</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04379</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04191</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04879</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04848</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02423</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03008</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04968</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.01249</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00197</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04971</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.02892</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01332</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04976</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03419</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.21487</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.35776</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.40181</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.4851</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38114</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38126</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.40433</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.9875700000000001</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.96274</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.47625</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.59741</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.47275</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.48716</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.5626599999999999</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.40456</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41343</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.43007</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.39341</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.41853</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.37512</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.41819</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.38177</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.39887</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42237</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.44209</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.46724</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.42986</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.38255</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.46902</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.99882</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.07245</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.9421</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.98248</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.36759</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.42942</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.20628</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.36708</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2864</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.37783</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.18471</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.18351</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.01451</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.007030000000000001</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.08422</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25397</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29162</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27438</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38436</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.39761</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36851</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32392</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.24988</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.41395</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.37573</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.49555</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.52128</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.39391</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.40714</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.48115</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.38732</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.43849</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.43163</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14049</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27432</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26996</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.29915</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29086</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39825</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33001</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.40621</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46914</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.41727</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.49177</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39082</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25479</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.27731</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.38772</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.47531</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41001</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.44671</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.40228</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.46971</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.57504</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37735</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.40084</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45884</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40131</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.3723399999999999</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40204</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23859</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36871</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47827</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40155</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40178</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39241</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37763</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3872</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.38789</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43108</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37675</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.30909</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26031</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3742799999999999</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.41889</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.38419</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42608</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42494</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.49475</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.57204</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5630299999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.4394</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.5690299999999999</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.62758</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49548</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.52273</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.56168</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.4716</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.61458</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.74019</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.70199</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.60721</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.53339</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5325800000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44126</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39619</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37726</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37289</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37009</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.36861</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.40814</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.36466</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.36476</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.38398</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38847</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.39908</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.40327</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.3779</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.14287</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.25394</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.2822</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.05852</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.13449</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.03123</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.20305</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.1549</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.007059999999999999</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.28483</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25824</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.14697</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05732</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.06695999999999999</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.18345</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.07202</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05517</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.21995</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15925</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.19175</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.36176</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.37439</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.39121</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.44169</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.40845</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.39908</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.48487</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.45028</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39086</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41611</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38964</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38425</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42191</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.42945</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38335</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38758</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.06769</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39825</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.57613</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.52173</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.4216</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.46583</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.41491</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.40166</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.39802</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.39864</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.38633</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.37756</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.37344</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37823</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38424</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.38221</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.15175</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.02555</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.02477</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.02263</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03259</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.27802</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.05043</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-3e-05</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01632</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.05429</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01238</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.00874</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.16222</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.05103</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.19368</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.40517</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.40343</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44048</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41399</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.42098</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38589</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.40227</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38266</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.40576</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36866</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37014</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.48515</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39919</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.38383</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.39223</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.40199</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.39016</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.38841</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38329</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.38289</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.38162</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.37366</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.18566</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.15505</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.21232</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.12366</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.23191</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04696</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.05246</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.05089</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.05062</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.05173</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.0487</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.10462</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03691</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.08491</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.1403</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.24305</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.28466</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16453</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.38588</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.16856</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.06358</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.21337</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.15358</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.26387</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.28333</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.40492</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38166</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.40384</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.38979</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38679</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.41064</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.4077</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4798</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.3944</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.39332</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.39774</v>
       </c>
     </row>
   </sheetData>
